--- a/prompt_engineering/ROADMAP.xlsx
+++ b/prompt_engineering/ROADMAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\prompt_engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF68B425-4A42-4283-858F-C5BE122A57AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED91A04C-0FC5-4037-80BE-DD800F086E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1605" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="210" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,11 +65,6 @@
     <t>Zero-Shot to Chain-of-Thought</t>
   </si>
   <si>
-    <t>• Few-Shot Prompting: Giving examples to set patterns.
-• Chain-of-Thought (CoT): Forcing AI to "show its work" (Critical for logic).
-• Role Prompting: "Act as a Senior Developer..."</t>
-  </si>
-  <si>
     <t>Project 2: "Logic Solver" (Solve a complex math riddle using CoT).</t>
   </si>
   <si>
@@ -157,6 +152,12 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>• Few-Shot Prompting: Giving examples to set patterns.
+• Chain-of-Thought (CoT): Forcing AI to "show its work" (Critical for logic).
+• Role Prompting: "Act as a Senior Developer..."
+• multistep prompting, iterative prompting</t>
   </si>
 </sst>
 </file>
@@ -306,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -333,9 +334,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,6 +614,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CF113114-11AC-45C5-8770-B7C05C1FC372}">
+  <we:reference id="wa200005669" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005669" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
@@ -635,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -661,10 +679,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
@@ -678,110 +696,110 @@
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="G3" s="3"/>
       <c r="I3" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="I4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="3"/>
-      <c r="I5" s="10" t="s">
-        <v>39</v>
+      <c r="I5" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/prompt_engineering/ROADMAP.xlsx
+++ b/prompt_engineering/ROADMAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\prompt_engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED91A04C-0FC5-4037-80BE-DD800F086E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51054680-56EF-4FA1-A13F-CE37209E94A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="210" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="180" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,11 +80,6 @@
     <t>Structured Outputs (JSON)</t>
   </si>
   <si>
-    <t>• Delimiters: Using ###, """, --- to separate data.
-• Format Constraint: Forcing JSON/Markdown for code integration.
-• Persona Adoption: Consistency in tone.</t>
-  </si>
-  <si>
     <t>Project 3: "Data Extractor" (Turn messy emails into clean JSON).</t>
   </si>
   <si>
@@ -154,10 +149,15 @@
     <t>done</t>
   </si>
   <si>
+    <t xml:space="preserve">• Delimiters: Using ###, """, --- to separate data.
+• Format Constraint: Forcing JSON/Markdown for code integration.
+</t>
+  </si>
+  <si>
     <t>• Few-Shot Prompting: Giving examples to set patterns.
 • Chain-of-Thought (CoT): Forcing AI to "show its work" (Critical for logic).
 • Role Prompting: "Act as a Senior Developer..."
-• multistep prompting, iterative prompting</t>
+• multistep prompting, iterative prompting , intruction prompting</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -679,7 +679,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -703,10 +703,10 @@
       </c>
       <c r="G3" s="3"/>
       <c r="I3" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
@@ -720,86 +720,86 @@
         <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="I4" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="3"/>
       <c r="I5" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
